--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -2,44 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2448689-87BA-4FFD-A6EB-8DA8E68FFA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD6F4A8-86B6-4295-AA1C-28326A8E509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="2160" windowWidth="21600" windowHeight="11385" xr2:uid="{B9C14B1B-B039-46FA-86D3-EF7E3BEC4BF4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Positionspriorität" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="31">
   <si>
     <t>Spieler</t>
   </si>
@@ -117,19 +99,32 @@
   </si>
   <si>
     <t>Tamino</t>
+  </si>
+  <si>
+    <t>Positionspriorität – U11 Coach</t>
+  </si>
+  <si>
+    <t>Bearbeitbar: Priorität 1 = bevorzugte Position. Änderungen hier können später direkt in den U11 Coach übernommen werden.</t>
+  </si>
+  <si>
+    <t>Priorität 1</t>
+  </si>
+  <si>
+    <t>Priorität 2</t>
+  </si>
+  <si>
+    <t>Priorität 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -144,16 +139,115 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF444444"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8102E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF222222"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -165,13 +259,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -188,6 +318,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PositionsPrioritaetTable" displayName="PositionsPrioritaetTable" ref="A4:D22" totalsRowShown="0">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Spieler"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Priorität 1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Priorität 2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Priorität 3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -233,108 +375,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -346,23 +394,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -372,23 +420,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -396,26 +444,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -450,17 +495,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -475,38 +520,13 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB283501-E44A-4ABA-AE5C-460E6A38FBD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1008,6 +1028,304 @@
       <c r="A20" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="B5:D22" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>"Torwart,Abwehr,Mittelfeld,Sturm,Spielmacher"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD6F4A8-86B6-4295-AA1C-28326A8E509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB77BC3-4C4F-42B1-BC74-5D6CF39C899E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
     <sheet name="Positionspriorität" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB77BC3-4C4F-42B1-BC74-5D6CF39C899E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AE34CA-7007-4A80-B0C8-75B936CC498D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -529,6 +529,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -567,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1">
         <v>4</v>
@@ -665,7 +669,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
@@ -821,7 +825,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="1">
         <v>6</v>

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AE34CA-7007-4A80-B0C8-75B936CC498D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BCF0FB-7F87-40CA-9D91-763A898D7736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spielerwerte" sheetId="1" r:id="rId1"/>
@@ -534,7 +534,7 @@
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +690,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -950,7 +950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">

--- a/Spielerwerte.xlsx
+++ b/Spielerwerte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fußball\Trainerarbeit\U11 Coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BCF0FB-7F87-40CA-9D91-763A898D7736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5F1443-025A-475F-9394-57298C4228C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1164,13 +1164,13 @@
         <v>14</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
